--- a/users.xlsx
+++ b/users.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\leo\Desktop\line bot\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68832F0F-0654-4761-8FDF-C312AC4FAA3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,13 +24,50 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+  <si>
+    <t>username</t>
+  </si>
+  <si>
+    <t>password</t>
+  </si>
+  <si>
+    <t>admin</t>
+  </si>
+  <si>
+    <t>leo</t>
+  </si>
+  <si>
+    <t>staff</t>
+  </si>
+  <si>
+    <t>staff123</t>
+  </si>
+  <si>
+    <t>manager</t>
+  </si>
+  <si>
+    <t>manager2026</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -49,11 +92,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="ปกติ" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -330,10 +382,55 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="17" customWidth="1"/>
+    <col min="2" max="2" width="16.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="1">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="1">
+        <v>9999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/users.xlsx
+++ b/users.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\leo\Desktop\line bot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68832F0F-0654-4761-8FDF-C312AC4FAA3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{514C0BE9-4DA1-40ED-8EEA-863CF8DAB352}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>username</t>
   </si>
@@ -43,12 +43,6 @@
   </si>
   <si>
     <t>staff123</t>
-  </si>
-  <si>
-    <t>manager</t>
-  </si>
-  <si>
-    <t>manager2026</t>
   </si>
 </sst>
 </file>
@@ -92,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -102,6 +96,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -383,7 +380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
@@ -423,11 +420,19 @@
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>7</v>
+      <c r="A5" s="3">
+        <v>1</v>
+      </c>
+      <c r="B5" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" s="4">
+        <v>2</v>
+      </c>
+      <c r="B6" s="1">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/users.xlsx
+++ b/users.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\leo\Desktop\line bot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{514C0BE9-4DA1-40ED-8EEA-863CF8DAB352}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB4EAFBE-4FEB-4947-B2BE-D12BDBD0B7E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -380,7 +380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
@@ -435,6 +435,14 @@
         <v>2</v>
       </c>
     </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" s="4">
+        <v>3</v>
+      </c>
+      <c r="B7" s="1">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/users.xlsx
+++ b/users.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\leo\Desktop\line bot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB4EAFBE-4FEB-4947-B2BE-D12BDBD0B7E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF9165E8-5BDE-47D1-8D7C-314426675A32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>username</t>
   </si>
@@ -43,6 +43,9 @@
   </si>
   <si>
     <t>staff123</t>
+  </si>
+  <si>
+    <t>TLE</t>
   </si>
 </sst>
 </file>
@@ -380,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
@@ -443,6 +446,14 @@
         <v>3</v>
       </c>
     </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="1">
+        <v>1801</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/users.xlsx
+++ b/users.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\leo\Desktop\line bot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF9165E8-5BDE-47D1-8D7C-314426675A32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50E7F404-549D-48AE-A917-5F43525A2F59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>username</t>
   </si>
@@ -46,6 +46,9 @@
   </si>
   <si>
     <t>TLE</t>
+  </si>
+  <si>
+    <t>status</t>
   </si>
 </sst>
 </file>
@@ -89,7 +92,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -101,6 +104,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -383,22 +389,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
     <col min="2" max="2" width="16.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C1" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -406,7 +415,7 @@
         <v>1234</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -414,7 +423,7 @@
         <v>9999</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -422,7 +431,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>1</v>
       </c>
@@ -430,7 +439,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
         <v>2</v>
       </c>
@@ -438,7 +447,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>3</v>
       </c>
@@ -446,7 +455,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
         <v>6</v>
       </c>
@@ -456,5 +465,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>